--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5BC55A6B-C566-4C96-95F1-AAA1F9B133DC}"/>
+  <xr:revisionPtr revIDLastSave="415" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5A86CD-586E-45EE-BBD0-C8902D21FBE1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -285,6 +285,21 @@
   <si>
     <t>Block out the final Sunday of every month to audit research progress, coursework grades, and personal well-being.</t>
   </si>
+  <si>
+    <t>Clone and run standard open-source baseline models in your domain to understand practical implementation hurdles early.</t>
+  </si>
+  <si>
+    <t>Set up tools like Weights &amp; Biases, MLflow, or structured lab notebooks to log hyperparameters, configurations, and raw outputs automatically.</t>
+  </si>
+  <si>
+    <t>Prepare structured meeting agendas, concise progress slides, and specific blocker questions rather than waiting for your advisor to request updates.</t>
+  </si>
+  <si>
+    <t>Connect with postdocs, affiliated faculty, or senior lab mentors who can provide day-to-day feedback on technical bottlenecks.</t>
+  </si>
+  <si>
+    <t>When reading literature, log key limitations, unaddressed edge cases, and implicit assumptions to spot viable gaps for novel research questions.</t>
+  </si>
 </sst>
 </file>
 
@@ -482,9 +497,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -497,30 +509,20 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1008,74 +1010,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
     </row>
     <row r="2" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
       <c r="E2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F2" s="21">
-        <v>1267262</v>
-      </c>
-      <c r="G2" s="21"/>
+      <c r="F2" s="25">
+        <v>12627223</v>
+      </c>
+      <c r="G2" s="25"/>
     </row>
     <row r="3" spans="1:23" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="21"/>
+      <c r="G3" s="25"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="23" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="23"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="23"/>
+      <c r="J4" s="23"/>
+      <c r="K4" s="23"/>
+      <c r="L4" s="23"/>
+      <c r="M4" s="23"/>
+      <c r="N4" s="23"/>
     </row>
     <row r="5" spans="1:23" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -1123,7 +1125,7 @@
     </row>
     <row r="6" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="B6" s="4">
         <v>400</v>
@@ -1169,7 +1171,7 @@
     </row>
     <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B7" s="8">
         <v>420</v>
@@ -1215,7 +1217,7 @@
     </row>
     <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="B8" s="8">
         <v>410</v>
@@ -1255,13 +1257,13 @@
       <c r="M8" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N8" s="25" t="s">
+      <c r="N8" s="22" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
-        <v>46247</v>
+        <v>46250</v>
       </c>
       <c r="B9" s="8">
         <v>440</v>
@@ -1301,7 +1303,7 @@
       <c r="M9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="24" t="s">
+      <c r="N9" s="21" t="s">
         <v>65</v>
       </c>
       <c r="R9" t="s">
@@ -1319,7 +1321,7 @@
     </row>
     <row r="10" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B10" s="8">
         <v>480</v>
@@ -1365,7 +1367,7 @@
     </row>
     <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="B11" s="8">
         <v>500</v>
@@ -1405,7 +1407,7 @@
       <c r="M11" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="22" t="s">
+      <c r="N11" s="19" t="s">
         <v>67</v>
       </c>
       <c r="Q11" t="s">
@@ -1432,7 +1434,7 @@
     </row>
     <row r="12" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
-        <v>46250</v>
+        <v>46253</v>
       </c>
       <c r="B12" s="8">
         <v>420</v>
@@ -1472,13 +1474,13 @@
       <c r="M12" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N12" s="23" t="s">
+      <c r="N12" s="20" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="B13" s="8">
         <v>420</v>
@@ -1518,13 +1520,13 @@
       <c r="M13" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="23" t="s">
+      <c r="N13" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
-        <v>46252</v>
+        <v>46255</v>
       </c>
       <c r="B14" s="8">
         <v>400</v>
@@ -1564,13 +1566,13 @@
       <c r="M14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N14" s="23" t="s">
+      <c r="N14" s="20" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="8">
         <v>420</v>
@@ -1610,13 +1612,13 @@
       <c r="M15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N15" s="23" t="s">
+      <c r="N15" s="20" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
-        <v>46254</v>
+        <v>46257</v>
       </c>
       <c r="B16" s="8">
         <v>480</v>
@@ -1656,13 +1658,13 @@
       <c r="M16" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="23" t="s">
+      <c r="N16" s="20" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B17" s="8">
         <v>450</v>
@@ -1702,13 +1704,13 @@
       <c r="M17" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N17" s="23" t="s">
+      <c r="N17" s="20" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B18" s="8">
         <v>420</v>
@@ -1748,13 +1750,13 @@
       <c r="M18" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N18" s="23" t="s">
+      <c r="N18" s="20" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B19" s="8">
         <v>450</v>
@@ -1794,13 +1796,13 @@
       <c r="M19" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N19" s="23" t="s">
+      <c r="N19" s="20" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B20" s="8">
         <v>480</v>
@@ -1840,13 +1842,13 @@
       <c r="M20" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N20" s="23" t="s">
+      <c r="N20" s="20" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B21" s="8">
         <v>420</v>
@@ -1886,13 +1888,13 @@
       <c r="M21" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N21" s="23" t="s">
+      <c r="N21" s="20" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B22" s="8">
         <v>400</v>
@@ -1932,13 +1934,13 @@
       <c r="M22" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N22" s="23" t="s">
+      <c r="N22" s="20" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B23" s="8">
         <v>420</v>
@@ -1978,13 +1980,13 @@
       <c r="M23" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N23" s="23" t="s">
+      <c r="N23" s="20" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B24" s="8">
         <v>415</v>
@@ -2024,13 +2026,13 @@
       <c r="M24" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="N24" s="23" t="s">
+      <c r="N24" s="20" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B25" s="8">
         <v>400</v>
@@ -2070,13 +2072,13 @@
       <c r="M25" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N25" s="23" t="s">
+      <c r="N25" s="20" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B26" s="8">
         <v>480</v>
@@ -2116,13 +2118,13 @@
       <c r="M26" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N26" s="23" t="s">
+      <c r="N26" s="20" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B27" s="8">
         <v>450</v>
@@ -2162,13 +2164,13 @@
       <c r="M27" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N27" s="23" t="s">
+      <c r="N27" s="20" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B28" s="8">
         <v>400</v>
@@ -2208,13 +2210,13 @@
       <c r="M28" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="23" t="s">
+      <c r="N28" s="20" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B29" s="8">
         <v>400</v>
@@ -2254,11 +2256,13 @@
       <c r="M29" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N29" s="11"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N29" s="22" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="B30" s="8">
         <v>480</v>
@@ -2298,11 +2302,13 @@
       <c r="M30" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N30" s="11"/>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N30" s="22" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B31" s="8">
         <v>480</v>
@@ -2342,11 +2348,13 @@
       <c r="M31" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="N31" s="11"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N31" s="22" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B32" s="8">
         <v>420</v>
@@ -2386,11 +2394,13 @@
       <c r="M32" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N32" s="11"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="N32" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="12">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B33" s="8">
         <v>420</v>
@@ -2430,11 +2440,13 @@
       <c r="M33" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="N33" s="11"/>
+      <c r="N33" s="22" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="12">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B34" s="8">
         <v>480</v>
@@ -2478,160 +2490,310 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="12">
-        <v>46272</v>
-      </c>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="9" t="str">
+        <v>46276</v>
+      </c>
+      <c r="B35" s="8">
+        <v>420</v>
+      </c>
+      <c r="C35" s="8">
+        <v>60</v>
+      </c>
+      <c r="D35" s="8">
+        <v>300</v>
+      </c>
+      <c r="E35" s="8">
+        <v>75</v>
+      </c>
+      <c r="F35" s="8">
+        <v>300</v>
+      </c>
+      <c r="G35" s="8">
+        <v>6</v>
+      </c>
+      <c r="H35" s="8">
+        <v>90</v>
+      </c>
+      <c r="I35" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="9" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J35" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
+        <v>195</v>
+      </c>
+      <c r="K35" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L35" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="N35" s="11"/>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="12">
-        <v>46273</v>
-      </c>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="9" t="str">
+        <v>46277</v>
+      </c>
+      <c r="B36" s="8">
+        <v>420</v>
+      </c>
+      <c r="C36" s="8">
+        <v>60</v>
+      </c>
+      <c r="D36" s="8">
+        <v>360</v>
+      </c>
+      <c r="E36" s="8">
+        <v>90</v>
+      </c>
+      <c r="F36" s="8">
+        <v>150</v>
+      </c>
+      <c r="G36" s="8">
+        <v>3</v>
+      </c>
+      <c r="H36" s="8">
+        <v>180</v>
+      </c>
+      <c r="I36" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="9" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J36" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="10"/>
-      <c r="L36" s="10"/>
-      <c r="M36" s="10"/>
+        <v>180</v>
+      </c>
+      <c r="K36" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L36" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M36" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="N36" s="11"/>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="12"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="9" t="str">
+      <c r="A37" s="12">
+        <v>46278</v>
+      </c>
+      <c r="B37" s="8">
+        <v>420</v>
+      </c>
+      <c r="C37" s="8">
+        <v>60</v>
+      </c>
+      <c r="D37" s="8">
+        <v>300</v>
+      </c>
+      <c r="E37" s="8">
+        <v>75</v>
+      </c>
+      <c r="F37" s="8">
+        <v>400</v>
+      </c>
+      <c r="G37" s="8">
+        <v>8</v>
+      </c>
+      <c r="H37" s="8">
+        <v>100</v>
+      </c>
+      <c r="I37" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="9" t="str">
+        <v>1355</v>
+      </c>
+      <c r="J37" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="10"/>
-      <c r="L37" s="10"/>
-      <c r="M37" s="10"/>
+        <v>85</v>
+      </c>
+      <c r="K37" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="N37" s="11"/>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="12"/>
-      <c r="B38" s="8"/>
-      <c r="C38" s="8"/>
-      <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8"/>
-      <c r="H38" s="8"/>
-      <c r="I38" s="9" t="str">
+      <c r="A38" s="12">
+        <v>46279</v>
+      </c>
+      <c r="B38" s="8">
+        <v>440</v>
+      </c>
+      <c r="C38" s="8">
+        <v>45</v>
+      </c>
+      <c r="D38" s="8">
+        <v>200</v>
+      </c>
+      <c r="E38" s="8">
+        <v>90</v>
+      </c>
+      <c r="F38" s="8">
+        <v>250</v>
+      </c>
+      <c r="G38" s="8">
+        <v>5</v>
+      </c>
+      <c r="H38" s="8">
+        <v>180</v>
+      </c>
+      <c r="I38" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="9" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J38" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="K38" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L38" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="N38" s="11"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="12"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="8"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8"/>
-      <c r="H39" s="8"/>
-      <c r="I39" s="9" t="str">
+      <c r="A39" s="12">
+        <v>46280</v>
+      </c>
+      <c r="B39" s="8">
+        <v>480</v>
+      </c>
+      <c r="C39" s="8">
+        <v>50</v>
+      </c>
+      <c r="D39" s="8">
+        <v>200</v>
+      </c>
+      <c r="E39" s="8">
+        <v>75</v>
+      </c>
+      <c r="F39" s="8">
+        <v>250</v>
+      </c>
+      <c r="G39" s="8">
+        <v>5</v>
+      </c>
+      <c r="H39" s="8">
+        <v>150</v>
+      </c>
+      <c r="I39" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="9" t="str">
+        <v>1205</v>
+      </c>
+      <c r="J39" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="10"/>
-      <c r="L39" s="10"/>
-      <c r="M39" s="10"/>
+        <v>235</v>
+      </c>
+      <c r="K39" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L39" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>59</v>
+      </c>
       <c r="N39" s="11"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8"/>
-      <c r="H40" s="8"/>
-      <c r="I40" s="9" t="str">
+      <c r="A40" s="12">
+        <v>46281</v>
+      </c>
+      <c r="B40" s="8">
+        <v>480</v>
+      </c>
+      <c r="C40" s="8">
+        <v>50</v>
+      </c>
+      <c r="D40" s="8">
+        <v>360</v>
+      </c>
+      <c r="E40" s="8">
+        <v>90</v>
+      </c>
+      <c r="F40" s="8">
+        <v>0</v>
+      </c>
+      <c r="G40" s="8">
+        <v>0</v>
+      </c>
+      <c r="H40" s="8">
+        <v>300</v>
+      </c>
+      <c r="I40" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="9" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J40" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="10"/>
-      <c r="L40" s="10"/>
-      <c r="M40" s="10"/>
+        <v>160</v>
+      </c>
+      <c r="K40" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L40" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="M40" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="N40" s="11"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="12"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8"/>
-      <c r="H41" s="8"/>
-      <c r="I41" s="9" t="str">
+      <c r="A41" s="12">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="8">
+        <v>440</v>
+      </c>
+      <c r="C41" s="8">
+        <v>80</v>
+      </c>
+      <c r="D41" s="8">
+        <v>300</v>
+      </c>
+      <c r="E41" s="8">
+        <v>100</v>
+      </c>
+      <c r="F41" s="8">
+        <v>0</v>
+      </c>
+      <c r="G41" s="8">
+        <v>0</v>
+      </c>
+      <c r="H41" s="8">
+        <v>300</v>
+      </c>
+      <c r="I41" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="9" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J41" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="10"/>
-      <c r="L41" s="10"/>
-      <c r="M41" s="10"/>
+        <v>220</v>
+      </c>
+      <c r="K41" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M41" s="10" t="s">
+        <v>55</v>
+      </c>
       <c r="N41" s="11"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
@@ -10564,7 +10726,7 @@
     <mergeCell ref="F3:G3"/>
   </mergeCells>
   <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="415" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5A86CD-586E-45EE-BBD0-C8902D21FBE1}"/>
+  <xr:revisionPtr revIDLastSave="469" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4B18FB-5CFD-4449-B504-313A6CE4EFC0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -158,9 +158,6 @@
   </si>
   <si>
     <t>Fitness (min)</t>
-  </si>
-  <si>
-    <t>Study (min)</t>
   </si>
   <si>
     <t>Coding (min)</t>
@@ -299,6 +296,9 @@
   </si>
   <si>
     <t>When reading literature, log key limitations, unaddressed edge cases, and implicit assumptions to spot viable gaps for novel research questions.</t>
+  </si>
+  <si>
+    <t>Study_(min)</t>
   </si>
 </sst>
 </file>
@@ -1090,37 +1090,37 @@
         <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="M5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -1157,24 +1157,24 @@
         <v>505</v>
       </c>
       <c r="K6" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="L6" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="M6" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="M6" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="N6" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>46248</v>
       </c>
-      <c r="B7" s="8">
-        <v>420</v>
+      <c r="B7" s="4">
+        <v>400</v>
       </c>
       <c r="C7" s="8">
         <v>60</v>
@@ -1196,31 +1196,31 @@
       </c>
       <c r="I7" s="9">
         <f t="shared" si="0"/>
-        <v>1065</v>
+        <v>1045</v>
       </c>
       <c r="J7" s="9">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>395</v>
       </c>
       <c r="K7" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M7" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>46249</v>
       </c>
-      <c r="B8" s="8">
-        <v>410</v>
+      <c r="B8" s="4">
+        <v>400</v>
       </c>
       <c r="C8" s="8">
         <v>60</v>
@@ -1242,31 +1242,31 @@
       </c>
       <c r="I8" s="9">
         <f t="shared" si="0"/>
-        <v>1125</v>
+        <v>1115</v>
       </c>
       <c r="J8" s="9">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="K8" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M8" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>46250</v>
       </c>
-      <c r="B9" s="8">
-        <v>440</v>
+      <c r="B9" s="4">
+        <v>400</v>
       </c>
       <c r="C9" s="8">
         <v>60</v>
@@ -1288,43 +1288,43 @@
       </c>
       <c r="I9" s="9">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1020</v>
       </c>
       <c r="J9" s="9">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>420</v>
       </c>
       <c r="K9" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M9" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N9" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="R9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="S9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="T9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>46251</v>
       </c>
-      <c r="B10" s="8">
-        <v>480</v>
+      <c r="B10" s="4">
+        <v>400</v>
       </c>
       <c r="C10" s="8">
         <v>60</v>
@@ -1346,31 +1346,31 @@
       </c>
       <c r="I10" s="9">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1030</v>
       </c>
       <c r="J10" s="9">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="K10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="N10" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>46252</v>
       </c>
-      <c r="B11" s="8">
-        <v>500</v>
+      <c r="B11" s="4">
+        <v>400</v>
       </c>
       <c r="C11" s="8">
         <v>60</v>
@@ -1392,52 +1392,52 @@
       </c>
       <c r="I11" s="9">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>850</v>
       </c>
       <c r="J11" s="9">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>590</v>
       </c>
       <c r="K11" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L11" s="10" t="s">
+      <c r="M11" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M11" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N11" s="19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="R11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="S11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="T11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="V11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="72" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>46253</v>
       </c>
-      <c r="B12" s="8">
-        <v>420</v>
+      <c r="B12" s="4">
+        <v>400</v>
       </c>
       <c r="C12" s="8">
         <v>60</v>
@@ -1459,31 +1459,31 @@
       </c>
       <c r="I12" s="9">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>900</v>
       </c>
       <c r="J12" s="9">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="K12" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L12" s="10" t="s">
+      <c r="M12" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M12" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N12" s="20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>46254</v>
       </c>
-      <c r="B13" s="8">
-        <v>420</v>
+      <c r="B13" s="4">
+        <v>400</v>
       </c>
       <c r="C13" s="8">
         <v>60</v>
@@ -1505,30 +1505,30 @@
       </c>
       <c r="I13" s="9">
         <f t="shared" si="0"/>
-        <v>1090</v>
+        <v>1070</v>
       </c>
       <c r="J13" s="9">
         <f t="shared" si="1"/>
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="K13" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L13" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L13" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M13" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N13" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>46255</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B14" s="4">
         <v>400</v>
       </c>
       <c r="C14" s="8">
@@ -1558,24 +1558,24 @@
         <v>390</v>
       </c>
       <c r="K14" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L14" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M14" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N14" s="20" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>46256</v>
       </c>
-      <c r="B15" s="8">
-        <v>420</v>
+      <c r="B15" s="4">
+        <v>400</v>
       </c>
       <c r="C15" s="8">
         <v>60</v>
@@ -1597,31 +1597,31 @@
       </c>
       <c r="I15" s="9">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="J15" s="9">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="K15" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="L15" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>61</v>
-      </c>
       <c r="N15" s="20" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>46257</v>
       </c>
-      <c r="B16" s="8">
-        <v>480</v>
+      <c r="B16" s="4">
+        <v>400</v>
       </c>
       <c r="C16" s="8">
         <v>60</v>
@@ -1643,31 +1643,31 @@
       </c>
       <c r="I16" s="9">
         <f t="shared" si="0"/>
-        <v>1110</v>
+        <v>1030</v>
       </c>
       <c r="J16" s="9">
         <f t="shared" si="1"/>
-        <v>330</v>
+        <v>410</v>
       </c>
       <c r="K16" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L16" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M16" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N16" s="20" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>46258</v>
       </c>
-      <c r="B17" s="8">
-        <v>450</v>
+      <c r="B17" s="4">
+        <v>400</v>
       </c>
       <c r="C17" s="8">
         <v>60</v>
@@ -1689,31 +1689,31 @@
       </c>
       <c r="I17" s="9">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1120</v>
       </c>
       <c r="J17" s="9">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>320</v>
       </c>
       <c r="K17" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L17" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M17" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" s="20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>46259</v>
       </c>
-      <c r="B18" s="8">
-        <v>420</v>
+      <c r="B18" s="4">
+        <v>400</v>
       </c>
       <c r="C18" s="8">
         <v>60</v>
@@ -1735,31 +1735,31 @@
       </c>
       <c r="I18" s="9">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1170</v>
       </c>
       <c r="J18" s="9">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="K18" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L18" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L18" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M18" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N18" s="20" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>46260</v>
       </c>
-      <c r="B19" s="8">
-        <v>450</v>
+      <c r="B19" s="4">
+        <v>400</v>
       </c>
       <c r="C19" s="8">
         <v>60</v>
@@ -1781,31 +1781,31 @@
       </c>
       <c r="I19" s="9">
         <f t="shared" si="0"/>
-        <v>1130</v>
+        <v>1080</v>
       </c>
       <c r="J19" s="9">
         <f t="shared" si="1"/>
-        <v>310</v>
+        <v>360</v>
       </c>
       <c r="K19" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L19" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L19" s="10" t="s">
+      <c r="M19" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M19" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N19" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>46261</v>
       </c>
-      <c r="B20" s="8">
-        <v>480</v>
+      <c r="B20" s="4">
+        <v>400</v>
       </c>
       <c r="C20" s="8">
         <v>60</v>
@@ -1827,31 +1827,31 @@
       </c>
       <c r="I20" s="9">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1060</v>
       </c>
       <c r="J20" s="9">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="K20" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L20" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L20" s="10" t="s">
+      <c r="M20" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M20" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N20" s="20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>46262</v>
       </c>
-      <c r="B21" s="8">
-        <v>420</v>
+      <c r="B21" s="4">
+        <v>400</v>
       </c>
       <c r="C21" s="8">
         <v>60</v>
@@ -1873,23 +1873,23 @@
       </c>
       <c r="I21" s="9">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="J21" s="9">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="K21" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L21" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L21" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M21" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1926,16 +1926,16 @@
         <v>390</v>
       </c>
       <c r="K22" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M22" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L22" s="10" t="s">
-        <v>57</v>
-      </c>
-      <c r="M22" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="N22" s="20" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1972,16 +1972,16 @@
         <v>285</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2018,16 +2018,16 @@
         <v>200</v>
       </c>
       <c r="K24" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L24" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L24" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M24" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N24" s="20" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2064,16 +2064,16 @@
         <v>335</v>
       </c>
       <c r="K25" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L25" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L25" s="10" t="s">
-        <v>54</v>
-      </c>
       <c r="M25" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2110,16 +2110,16 @@
         <v>390</v>
       </c>
       <c r="K26" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L26" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L26" s="10" t="s">
+      <c r="M26" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N26" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2156,16 +2156,16 @@
         <v>380</v>
       </c>
       <c r="K27" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L27" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L27" s="10" t="s">
+      <c r="M27" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M27" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N27" s="20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2202,16 +2202,16 @@
         <v>240</v>
       </c>
       <c r="K28" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L28" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L28" s="10" t="s">
+      <c r="M28" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="M28" s="10" t="s">
-        <v>55</v>
-      </c>
       <c r="N28" s="20" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2248,16 +2248,16 @@
         <v>430</v>
       </c>
       <c r="K29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L29" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M29" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="N29" s="22" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
@@ -2294,16 +2294,16 @@
         <v>185</v>
       </c>
       <c r="K30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="L30" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M30" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="L30" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>59</v>
-      </c>
       <c r="N30" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2340,16 +2340,16 @@
         <v>370</v>
       </c>
       <c r="K31" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L31" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M31" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N31" s="22" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2386,16 +2386,16 @@
         <v>360</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N32" s="22" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2432,16 +2432,16 @@
         <v>290</v>
       </c>
       <c r="K33" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L33" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L33" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M33" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N33" s="22" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2478,13 +2478,13 @@
         <v>245</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N34" s="11"/>
     </row>
@@ -2522,13 +2522,13 @@
         <v>195</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N35" s="11"/>
     </row>
@@ -2566,13 +2566,13 @@
         <v>180</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L36" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M36" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="M36" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="N36" s="11"/>
     </row>
@@ -2610,13 +2610,13 @@
         <v>85</v>
       </c>
       <c r="K37" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L37" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="L37" s="10" t="s">
+      <c r="M37" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="N37" s="11"/>
     </row>
@@ -2654,13 +2654,13 @@
         <v>235</v>
       </c>
       <c r="K38" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L38" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L38" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M38" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N38" s="11"/>
     </row>
@@ -2698,13 +2698,13 @@
         <v>235</v>
       </c>
       <c r="K39" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L39" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L39" s="10" t="s">
-        <v>57</v>
-      </c>
       <c r="M39" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N39" s="11"/>
     </row>
@@ -2742,13 +2742,13 @@
         <v>160</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L40" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M40" s="10" t="s">
         <v>54</v>
-      </c>
-      <c r="M40" s="10" t="s">
-        <v>55</v>
       </c>
       <c r="N40" s="11"/>
     </row>
@@ -2786,102 +2786,190 @@
         <v>220</v>
       </c>
       <c r="K41" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L41" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="L41" s="10" t="s">
+      <c r="M41" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N41" s="11"/>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A42" s="12">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="8">
+        <v>420</v>
+      </c>
+      <c r="C42" s="8">
+        <v>60</v>
+      </c>
+      <c r="D42" s="8">
+        <v>240</v>
+      </c>
+      <c r="E42" s="8">
+        <v>60</v>
+      </c>
+      <c r="F42" s="8">
+        <v>300</v>
+      </c>
+      <c r="G42" s="8">
+        <v>6</v>
+      </c>
+      <c r="H42" s="8">
+        <v>90</v>
+      </c>
+      <c r="I42" s="9">
+        <f t="shared" si="0"/>
+        <v>1170</v>
+      </c>
+      <c r="J42" s="9">
+        <f t="shared" si="1"/>
+        <v>270</v>
+      </c>
+      <c r="K42" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L42" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="N42" s="11"/>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A43" s="12">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="8">
+        <v>450</v>
+      </c>
+      <c r="C43" s="8">
+        <v>90</v>
+      </c>
+      <c r="D43" s="8">
+        <v>180</v>
+      </c>
+      <c r="E43" s="8">
+        <v>70</v>
+      </c>
+      <c r="F43" s="8">
+        <v>150</v>
+      </c>
+      <c r="G43" s="8">
+        <v>3</v>
+      </c>
+      <c r="H43" s="8">
+        <v>120</v>
+      </c>
+      <c r="I43" s="9">
+        <f t="shared" si="0"/>
+        <v>1060</v>
+      </c>
+      <c r="J43" s="9">
+        <f t="shared" si="1"/>
+        <v>380</v>
+      </c>
+      <c r="K43" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L43" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M43" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="N43" s="11"/>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A44" s="12">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="8">
+        <v>480</v>
+      </c>
+      <c r="C44" s="8">
+        <v>60</v>
+      </c>
+      <c r="D44" s="8">
+        <v>190</v>
+      </c>
+      <c r="E44" s="8">
+        <v>60</v>
+      </c>
+      <c r="F44" s="8">
+        <v>400</v>
+      </c>
+      <c r="G44" s="8">
+        <v>8</v>
+      </c>
+      <c r="H44" s="8">
+        <v>60</v>
+      </c>
+      <c r="I44" s="9">
+        <f t="shared" si="0"/>
+        <v>1250</v>
+      </c>
+      <c r="J44" s="9">
+        <f t="shared" si="1"/>
+        <v>190</v>
+      </c>
+      <c r="K44" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L44" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="M41" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="N41" s="11"/>
-    </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="12"/>
-      <c r="B42" s="8"/>
-      <c r="C42" s="8"/>
-      <c r="D42" s="8"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8"/>
-      <c r="H42" s="8"/>
-      <c r="I42" s="9" t="str">
+      <c r="M44" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="N44" s="11"/>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A45" s="12">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="8">
+        <v>400</v>
+      </c>
+      <c r="C45" s="8">
+        <v>60</v>
+      </c>
+      <c r="D45" s="8">
+        <v>180</v>
+      </c>
+      <c r="E45" s="8">
+        <v>75</v>
+      </c>
+      <c r="F45" s="8">
+        <v>250</v>
+      </c>
+      <c r="G45" s="8">
+        <v>5</v>
+      </c>
+      <c r="H45" s="8">
+        <v>90</v>
+      </c>
+      <c r="I45" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="9" t="str">
+        <v>1055</v>
+      </c>
+      <c r="J45" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="10"/>
-      <c r="L42" s="10"/>
-      <c r="M42" s="10"/>
-      <c r="N42" s="11"/>
-    </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="12"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8"/>
-      <c r="H43" s="8"/>
-      <c r="I43" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="10"/>
-      <c r="L43" s="10"/>
-      <c r="M43" s="10"/>
-      <c r="N43" s="11"/>
-    </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="12"/>
-      <c r="B44" s="8"/>
-      <c r="C44" s="8"/>
-      <c r="D44" s="8"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8"/>
-      <c r="H44" s="8"/>
-      <c r="I44" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="11"/>
-    </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="12"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8"/>
-      <c r="H45" s="8"/>
-      <c r="I45" s="9" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="9" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="10"/>
-      <c r="L45" s="10"/>
-      <c r="M45" s="10"/>
+        <v>385</v>
+      </c>
+      <c r="K45" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L45" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M45" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="469" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4B18FB-5CFD-4449-B504-313A6CE4EFC0}"/>
+  <xr:revisionPtr revIDLastSave="505" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8401A89-B4C4-4A38-A00C-64D07C108713}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2973,69 +2973,135 @@
       <c r="N45" s="11"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="12"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="8"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="9" t="str">
+      <c r="A46" s="12">
+        <v>46287</v>
+      </c>
+      <c r="B46" s="8">
+        <v>400</v>
+      </c>
+      <c r="C46" s="8">
+        <v>60</v>
+      </c>
+      <c r="D46" s="8">
+        <v>180</v>
+      </c>
+      <c r="E46" s="8">
+        <v>60</v>
+      </c>
+      <c r="F46" s="8">
+        <v>250</v>
+      </c>
+      <c r="G46" s="8">
+        <v>5</v>
+      </c>
+      <c r="H46" s="8">
+        <v>120</v>
+      </c>
+      <c r="I46" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="9" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J46" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="10"/>
-      <c r="L46" s="10"/>
-      <c r="M46" s="10"/>
+        <v>370</v>
+      </c>
+      <c r="K46" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L46" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="M46" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="N46" s="11"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="12"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="9" t="str">
+      <c r="A47" s="12">
+        <v>46288</v>
+      </c>
+      <c r="B47" s="8">
+        <v>420</v>
+      </c>
+      <c r="C47" s="8">
+        <v>60</v>
+      </c>
+      <c r="D47" s="8">
+        <v>180</v>
+      </c>
+      <c r="E47" s="8">
+        <v>90</v>
+      </c>
+      <c r="F47" s="8">
+        <v>0</v>
+      </c>
+      <c r="G47" s="8">
+        <v>0</v>
+      </c>
+      <c r="H47" s="8">
+        <v>180</v>
+      </c>
+      <c r="I47" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="9" t="str">
+        <v>930</v>
+      </c>
+      <c r="J47" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="10"/>
-      <c r="L47" s="10"/>
-      <c r="M47" s="10"/>
+        <v>510</v>
+      </c>
+      <c r="K47" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L47" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M47" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="N47" s="11"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="12"/>
-      <c r="B48" s="8"/>
-      <c r="C48" s="8"/>
-      <c r="D48" s="8"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="8"/>
-      <c r="H48" s="8"/>
-      <c r="I48" s="9" t="str">
+      <c r="A48" s="12">
+        <v>46289</v>
+      </c>
+      <c r="B48" s="8">
+        <v>480</v>
+      </c>
+      <c r="C48" s="8">
+        <v>60</v>
+      </c>
+      <c r="D48" s="8">
+        <v>300</v>
+      </c>
+      <c r="E48" s="8">
+        <v>90</v>
+      </c>
+      <c r="F48" s="8">
+        <v>0</v>
+      </c>
+      <c r="G48" s="8">
+        <v>0</v>
+      </c>
+      <c r="H48" s="8">
+        <v>180</v>
+      </c>
+      <c r="I48" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="9" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J48" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="10"/>
-      <c r="L48" s="10"/>
-      <c r="M48" s="10"/>
+        <v>330</v>
+      </c>
+      <c r="K48" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L48" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="M48" s="10" t="s">
+        <v>54</v>
+      </c>
       <c r="N48" s="11"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="505" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8401A89-B4C4-4A38-A00C-64D07C108713}"/>
+  <xr:revisionPtr revIDLastSave="518" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AECF9563-2F83-4AEB-B9C3-2C96157D449F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3105,25 +3105,47 @@
       <c r="N48" s="11"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="12"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
-      <c r="D49" s="8"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
-      <c r="I49" s="9" t="str">
+      <c r="A49" s="12">
+        <v>46290</v>
+      </c>
+      <c r="B49" s="8">
+        <v>480</v>
+      </c>
+      <c r="C49" s="8">
+        <v>60</v>
+      </c>
+      <c r="D49" s="8">
+        <v>300</v>
+      </c>
+      <c r="E49" s="8">
+        <v>60</v>
+      </c>
+      <c r="F49" s="8">
+        <v>6</v>
+      </c>
+      <c r="G49" s="8">
+        <v>300</v>
+      </c>
+      <c r="H49" s="8">
+        <v>90</v>
+      </c>
+      <c r="I49" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="9" t="str">
+        <v>996</v>
+      </c>
+      <c r="J49" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="10"/>
-      <c r="L49" s="10"/>
-      <c r="M49" s="10"/>
+        <v>444</v>
+      </c>
+      <c r="K49" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="L49" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="M49" s="10" t="s">
+        <v>58</v>
+      </c>
       <c r="N49" s="11"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="518" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AECF9563-2F83-4AEB-B9C3-2C96157D449F}"/>
+  <xr:revisionPtr revIDLastSave="552" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E7E9EE-F2E8-486A-B6FD-0B75B7E88A81}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -148,43 +148,7 @@
     <t>August to December</t>
   </si>
   <si>
-    <t>All durations in MINUTES. Yellow cells = enter your data. Row 6 is a sample — overwrite it. Rows 2-3: fill your details.</t>
-  </si>
-  <si>
     <t>Date</t>
-  </si>
-  <si>
-    <t>Sleep (min)</t>
-  </si>
-  <si>
-    <t>Fitness (min)</t>
-  </si>
-  <si>
-    <t>Coding (min)</t>
-  </si>
-  <si>
-    <t>Class (min)</t>
-  </si>
-  <si>
-    <t>Classes Attended</t>
-  </si>
-  <si>
-    <t>Other Activities (min)</t>
-  </si>
-  <si>
-    <t>Total Tracked (min)</t>
-  </si>
-  <si>
-    <t>Free/Unaccounted (min)</t>
-  </si>
-  <si>
-    <t>Day's Feeling</t>
-  </si>
-  <si>
-    <t>Satisfaction Level</t>
-  </si>
-  <si>
-    <t>Energy Level</t>
   </si>
   <si>
     <t>Notes</t>
@@ -298,7 +262,43 @@
     <t>When reading literature, log key limitations, unaddressed edge cases, and implicit assumptions to spot viable gaps for novel research questions.</t>
   </si>
   <si>
-    <t>Study_(min)</t>
+    <t>Classes_Attended</t>
+  </si>
+  <si>
+    <t>Day'sFeeling</t>
+  </si>
+  <si>
+    <t>Satisfaction_Level</t>
+  </si>
+  <si>
+    <t>Energy_Level</t>
+  </si>
+  <si>
+    <t>Sleep_min</t>
+  </si>
+  <si>
+    <t>Fitness_min</t>
+  </si>
+  <si>
+    <t>Study_min</t>
+  </si>
+  <si>
+    <t>Coding_min</t>
+  </si>
+  <si>
+    <t>Class_min</t>
+  </si>
+  <si>
+    <t>Other_Activities _min</t>
+  </si>
+  <si>
+    <t>Total_Tracked_min</t>
+  </si>
+  <si>
+    <t>Free/Unaccounted_min</t>
+  </si>
+  <si>
+    <t>aa</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B4" s="23"/>
       <c r="C4" s="23"/>
@@ -1079,48 +1079,48 @@
       <c r="M4" s="23"/>
       <c r="N4" s="23"/>
     </row>
-    <row r="5" spans="1:23" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:23" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N5" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -1157,16 +1157,16 @@
         <v>505</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N6" s="7" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -1203,16 +1203,16 @@
         <v>395</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M7" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N7" s="18" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1249,16 +1249,16 @@
         <v>325</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N8" s="22" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1295,28 +1295,28 @@
         <v>420</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N9" s="21" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="R9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="S9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="T9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="U9" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1353,16 +1353,16 @@
         <v>410</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -1399,37 +1399,37 @@
         <v>590</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L11" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M11" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N11" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="N11" s="19" t="s">
-        <v>66</v>
-      </c>
       <c r="Q11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="R11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="S11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="T11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="U11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="V11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="W11" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="72" x14ac:dyDescent="0.3">
@@ -1466,16 +1466,16 @@
         <v>540</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L12" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N12" s="20" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -1512,16 +1512,16 @@
         <v>370</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L13" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N13" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="N13" s="20" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:23" ht="43.2" x14ac:dyDescent="0.3">
@@ -1558,16 +1558,16 @@
         <v>390</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L14" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="N14" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="M14" s="10" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="20" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1604,16 +1604,16 @@
         <v>320</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="N15" s="20" t="s">
         <v>57</v>
-      </c>
-      <c r="M15" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="N15" s="20" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="57.6" x14ac:dyDescent="0.3">
@@ -1650,16 +1650,16 @@
         <v>410</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L16" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N16" s="20" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1696,16 +1696,16 @@
         <v>320</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N17" s="20" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1742,16 +1742,16 @@
         <v>270</v>
       </c>
       <c r="K18" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L18" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N18" s="20" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1788,16 +1788,16 @@
         <v>360</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N19" s="20" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1834,16 +1834,16 @@
         <v>380</v>
       </c>
       <c r="K20" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L20" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N20" s="20" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1880,16 +1880,16 @@
         <v>320</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L21" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N21" s="20" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1926,16 +1926,16 @@
         <v>390</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L22" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M22" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N22" s="20" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -1972,16 +1972,16 @@
         <v>285</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L23" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M23" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N23" s="20" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2018,16 +2018,16 @@
         <v>200</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L24" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N24" s="20" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2064,16 +2064,16 @@
         <v>335</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L25" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M25" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N25" s="20" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2110,16 +2110,16 @@
         <v>390</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L26" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M26" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N26" s="20" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2156,16 +2156,16 @@
         <v>380</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M27" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N27" s="20" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2202,16 +2202,16 @@
         <v>240</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M28" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N28" s="20" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -2248,16 +2248,16 @@
         <v>430</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M29" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N29" s="22" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="86.4" x14ac:dyDescent="0.3">
@@ -2294,16 +2294,16 @@
         <v>185</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M30" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N30" s="22" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2340,16 +2340,16 @@
         <v>370</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M31" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N31" s="22" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2386,16 +2386,16 @@
         <v>360</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N32" s="22" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="72" x14ac:dyDescent="0.3">
@@ -2432,16 +2432,16 @@
         <v>290</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L33" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M33" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N33" s="22" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
@@ -2478,13 +2478,13 @@
         <v>245</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M34" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N34" s="11"/>
     </row>
@@ -2522,13 +2522,13 @@
         <v>195</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M35" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N35" s="11"/>
     </row>
@@ -2566,13 +2566,13 @@
         <v>180</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M36" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N36" s="11"/>
     </row>
@@ -2610,13 +2610,13 @@
         <v>85</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M37" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N37" s="11"/>
     </row>
@@ -2654,13 +2654,13 @@
         <v>235</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M38" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N38" s="11"/>
     </row>
@@ -2698,13 +2698,13 @@
         <v>235</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M39" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N39" s="11"/>
     </row>
@@ -2742,13 +2742,13 @@
         <v>160</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M40" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N40" s="11"/>
     </row>
@@ -2786,13 +2786,13 @@
         <v>220</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M41" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N41" s="11"/>
     </row>
@@ -2830,13 +2830,13 @@
         <v>270</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N42" s="11"/>
     </row>
@@ -2874,13 +2874,13 @@
         <v>380</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M43" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N43" s="11"/>
     </row>
@@ -2918,13 +2918,13 @@
         <v>190</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M44" s="10" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N44" s="11"/>
     </row>
@@ -2962,13 +2962,13 @@
         <v>385</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M45" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N45" s="11"/>
     </row>
@@ -3006,13 +3006,13 @@
         <v>370</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N46" s="11"/>
     </row>
@@ -3050,13 +3050,13 @@
         <v>510</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M47" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N47" s="11"/>
     </row>
@@ -3094,13 +3094,13 @@
         <v>330</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="N48" s="11"/>
     </row>
@@ -3138,36 +3138,58 @@
         <v>444</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="N49" s="11"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="12"/>
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="9" t="str">
+      <c r="A50" s="12">
+        <v>46291</v>
+      </c>
+      <c r="B50" s="8">
+        <v>480</v>
+      </c>
+      <c r="C50" s="8">
+        <v>60</v>
+      </c>
+      <c r="D50" s="8">
+        <v>300</v>
+      </c>
+      <c r="E50" s="8">
+        <v>75</v>
+      </c>
+      <c r="F50" s="8">
+        <v>3</v>
+      </c>
+      <c r="G50" s="8">
+        <v>150</v>
+      </c>
+      <c r="H50" s="8">
+        <v>90</v>
+      </c>
+      <c r="I50" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="9" t="str">
+        <v>1008</v>
+      </c>
+      <c r="J50" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="10"/>
-      <c r="L50" s="10"/>
-      <c r="M50" s="10"/>
+        <v>432</v>
+      </c>
+      <c r="K50" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L50" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M50" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="N50" s="11"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="552" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E7E9EE-F2E8-486A-B6FD-0B75B7E88A81}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2080486-2629-4CE0-A76E-1A8C1D217C77}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3193,25 +3193,47 @@
       <c r="N50" s="11"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="12"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="9" t="str">
+      <c r="A51" s="12">
+        <v>46292</v>
+      </c>
+      <c r="B51" s="8">
+        <v>480</v>
+      </c>
+      <c r="C51" s="8">
+        <v>60</v>
+      </c>
+      <c r="D51" s="8">
+        <v>200</v>
+      </c>
+      <c r="E51" s="8">
+        <v>60</v>
+      </c>
+      <c r="F51" s="8">
+        <v>5</v>
+      </c>
+      <c r="G51" s="8">
+        <v>250</v>
+      </c>
+      <c r="H51" s="8">
+        <v>90</v>
+      </c>
+      <c r="I51" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="9" t="str">
+        <v>895</v>
+      </c>
+      <c r="J51" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="10"/>
-      <c r="L51" s="10"/>
-      <c r="M51" s="10"/>
+        <v>545</v>
+      </c>
+      <c r="K51" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L51" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M51" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="N51" s="11"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2080486-2629-4CE0-A76E-1A8C1D217C77}"/>
+  <xr:revisionPtr revIDLastSave="587" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C321468-691C-4C21-B53A-AD7E23357A82}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3237,47 +3237,91 @@
       <c r="N51" s="11"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="12"/>
-      <c r="B52" s="8"/>
-      <c r="C52" s="8"/>
-      <c r="D52" s="8"/>
-      <c r="E52" s="8"/>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8"/>
-      <c r="H52" s="8"/>
-      <c r="I52" s="9" t="str">
+      <c r="A52" s="12">
+        <v>46293</v>
+      </c>
+      <c r="B52" s="8">
+        <v>480</v>
+      </c>
+      <c r="C52" s="8">
+        <v>60</v>
+      </c>
+      <c r="D52" s="8">
+        <v>120</v>
+      </c>
+      <c r="E52" s="8">
+        <v>0</v>
+      </c>
+      <c r="F52" s="8">
+        <v>0</v>
+      </c>
+      <c r="G52" s="8">
+        <v>0</v>
+      </c>
+      <c r="H52" s="8">
+        <v>400</v>
+      </c>
+      <c r="I52" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="9" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J52" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="10"/>
-      <c r="L52" s="10"/>
-      <c r="M52" s="10"/>
+        <v>380</v>
+      </c>
+      <c r="K52" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L52" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N52" s="11"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="12"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8"/>
-      <c r="H53" s="8"/>
-      <c r="I53" s="9" t="str">
+      <c r="A53" s="12">
+        <v>46294</v>
+      </c>
+      <c r="B53" s="8">
+        <v>240</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0</v>
+      </c>
+      <c r="D53" s="8">
+        <v>0</v>
+      </c>
+      <c r="E53" s="8">
+        <v>0</v>
+      </c>
+      <c r="F53" s="8">
+        <v>0</v>
+      </c>
+      <c r="G53" s="8">
+        <v>0</v>
+      </c>
+      <c r="H53" s="8">
+        <v>500</v>
+      </c>
+      <c r="I53" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="9" t="str">
+        <v>740</v>
+      </c>
+      <c r="J53" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="10"/>
-      <c r="L53" s="10"/>
-      <c r="M53" s="10"/>
+        <v>700</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L53" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M53" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N53" s="11"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="587" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C321468-691C-4C21-B53A-AD7E23357A82}"/>
+  <xr:revisionPtr revIDLastSave="599" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CEDFD3-1A58-4BF0-906E-0AE3F8DB7832}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3325,25 +3325,47 @@
       <c r="N53" s="11"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="12"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8"/>
-      <c r="H54" s="8"/>
-      <c r="I54" s="9" t="str">
+      <c r="A54" s="12">
+        <v>46295</v>
+      </c>
+      <c r="B54" s="8">
+        <v>600</v>
+      </c>
+      <c r="C54" s="8">
+        <v>60</v>
+      </c>
+      <c r="D54" s="8">
+        <v>140</v>
+      </c>
+      <c r="E54" s="8">
+        <v>60</v>
+      </c>
+      <c r="F54" s="8">
+        <v>0</v>
+      </c>
+      <c r="G54" s="8">
+        <v>0</v>
+      </c>
+      <c r="H54" s="8">
+        <v>500</v>
+      </c>
+      <c r="I54" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="9" t="str">
+        <v>1360</v>
+      </c>
+      <c r="J54" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="10"/>
-      <c r="L54" s="10"/>
-      <c r="M54" s="10"/>
+        <v>80</v>
+      </c>
+      <c r="K54" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L54" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N54" s="11"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="599" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92CEDFD3-1A58-4BF0-906E-0AE3F8DB7832}"/>
+  <xr:revisionPtr revIDLastSave="610" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91816EB9-1E2E-44DE-B362-189E2F658C7A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3369,25 +3369,47 @@
       <c r="N54" s="11"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="12"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="8"/>
-      <c r="G55" s="8"/>
-      <c r="H55" s="8"/>
-      <c r="I55" s="9" t="str">
+      <c r="A55" s="12">
+        <v>46296</v>
+      </c>
+      <c r="B55" s="8">
+        <v>480</v>
+      </c>
+      <c r="C55" s="8">
+        <v>60</v>
+      </c>
+      <c r="D55" s="8">
+        <v>240</v>
+      </c>
+      <c r="E55" s="8">
+        <v>60</v>
+      </c>
+      <c r="F55" s="8">
+        <v>0</v>
+      </c>
+      <c r="G55" s="8">
+        <v>0</v>
+      </c>
+      <c r="H55" s="8">
+        <v>450</v>
+      </c>
+      <c r="I55" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="9" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J55" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
+        <v>150</v>
+      </c>
+      <c r="K55" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L55" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M55" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N55" s="11"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="610" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91816EB9-1E2E-44DE-B362-189E2F658C7A}"/>
+  <xr:revisionPtr revIDLastSave="622" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4227BB-12F8-4EC3-9CC3-996EA830ECDA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3413,25 +3413,47 @@
       <c r="N55" s="11"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="12"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8"/>
-      <c r="I56" s="9" t="str">
+      <c r="A56" s="12">
+        <v>46297</v>
+      </c>
+      <c r="B56" s="8">
+        <v>480</v>
+      </c>
+      <c r="C56" s="8">
+        <v>60</v>
+      </c>
+      <c r="D56" s="8">
+        <v>200</v>
+      </c>
+      <c r="E56" s="8">
+        <v>60</v>
+      </c>
+      <c r="F56" s="8">
+        <v>0</v>
+      </c>
+      <c r="G56" s="8">
+        <v>0</v>
+      </c>
+      <c r="H56" s="8">
+        <v>500</v>
+      </c>
+      <c r="I56" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="9" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J56" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="10"/>
-      <c r="L56" s="10"/>
-      <c r="M56" s="10"/>
+        <v>140</v>
+      </c>
+      <c r="K56" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L56" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M56" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N56" s="11"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="622" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4227BB-12F8-4EC3-9CC3-996EA830ECDA}"/>
+  <xr:revisionPtr revIDLastSave="635" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD161E7-2832-41FC-8526-BE35893EE1E0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3457,25 +3457,47 @@
       <c r="N56" s="11"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="12"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
-      <c r="F57" s="8"/>
-      <c r="G57" s="8"/>
-      <c r="H57" s="8"/>
-      <c r="I57" s="9" t="str">
+      <c r="A57" s="12">
+        <v>46298</v>
+      </c>
+      <c r="B57" s="8">
+        <v>480</v>
+      </c>
+      <c r="C57" s="8">
+        <v>75</v>
+      </c>
+      <c r="D57" s="8">
+        <v>180</v>
+      </c>
+      <c r="E57" s="8">
+        <v>75</v>
+      </c>
+      <c r="F57" s="8">
+        <v>0</v>
+      </c>
+      <c r="G57" s="8">
+        <v>0</v>
+      </c>
+      <c r="H57" s="8">
+        <v>350</v>
+      </c>
+      <c r="I57" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="9" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J57" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="10"/>
-      <c r="L57" s="10"/>
-      <c r="M57" s="10"/>
+        <v>280</v>
+      </c>
+      <c r="K57" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L57" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M57" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="635" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD161E7-2832-41FC-8526-BE35893EE1E0}"/>
+  <xr:revisionPtr revIDLastSave="647" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{897C043C-1F70-47E7-B458-F845B4650C32}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3501,25 +3501,47 @@
       <c r="N57" s="11"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="12"/>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="9" t="str">
+      <c r="A58" s="12">
+        <v>46299</v>
+      </c>
+      <c r="B58" s="8">
+        <v>480</v>
+      </c>
+      <c r="C58" s="8">
+        <v>75</v>
+      </c>
+      <c r="D58" s="8">
+        <v>200</v>
+      </c>
+      <c r="E58" s="8">
+        <v>60</v>
+      </c>
+      <c r="F58" s="8">
+        <v>0</v>
+      </c>
+      <c r="G58" s="8">
+        <v>0</v>
+      </c>
+      <c r="H58" s="8">
+        <v>400</v>
+      </c>
+      <c r="I58" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="9" t="str">
+        <v>1215</v>
+      </c>
+      <c r="J58" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="10"/>
-      <c r="L58" s="10"/>
-      <c r="M58" s="10"/>
+        <v>225</v>
+      </c>
+      <c r="K58" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L58" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N58" s="11"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="647" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{897C043C-1F70-47E7-B458-F845B4650C32}"/>
+  <xr:revisionPtr revIDLastSave="659" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DA2346C-782A-431C-81A0-3F327CA39D5A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3545,25 +3545,47 @@
       <c r="N58" s="11"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="12"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="9" t="str">
+      <c r="A59" s="12">
+        <v>46300</v>
+      </c>
+      <c r="B59" s="8">
+        <v>480</v>
+      </c>
+      <c r="C59" s="8">
+        <v>70</v>
+      </c>
+      <c r="D59" s="8">
+        <v>200</v>
+      </c>
+      <c r="E59" s="8">
+        <v>75</v>
+      </c>
+      <c r="F59" s="8">
+        <v>0</v>
+      </c>
+      <c r="G59" s="8">
+        <v>0</v>
+      </c>
+      <c r="H59" s="8">
+        <v>420</v>
+      </c>
+      <c r="I59" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="9" t="str">
+        <v>1245</v>
+      </c>
+      <c r="J59" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="10"/>
-      <c r="L59" s="10"/>
-      <c r="M59" s="10"/>
+        <v>195</v>
+      </c>
+      <c r="K59" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L59" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N59" s="11"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="659" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DA2346C-782A-431C-81A0-3F327CA39D5A}"/>
+  <xr:revisionPtr revIDLastSave="675" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA215080-4127-42AE-99BD-1A0BBDB3E1B0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3561,21 +3561,21 @@
         <v>75</v>
       </c>
       <c r="F59" s="8">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G59" s="8">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H59" s="8">
-        <v>420</v>
+        <v>180</v>
       </c>
       <c r="I59" s="9">
         <f t="shared" si="0"/>
-        <v>1245</v>
+        <v>1305</v>
       </c>
       <c r="J59" s="9">
         <f t="shared" si="1"/>
-        <v>195</v>
+        <v>135</v>
       </c>
       <c r="K59" s="10" t="s">
         <v>40</v>
@@ -3589,25 +3589,47 @@
       <c r="N59" s="11"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="12"/>
-      <c r="B60" s="8"/>
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="9" t="str">
+      <c r="A60" s="12">
+        <v>46301</v>
+      </c>
+      <c r="B60" s="8">
+        <v>500</v>
+      </c>
+      <c r="C60" s="8">
+        <v>70</v>
+      </c>
+      <c r="D60" s="8">
+        <v>180</v>
+      </c>
+      <c r="E60" s="8">
+        <v>60</v>
+      </c>
+      <c r="F60" s="8">
+        <v>150</v>
+      </c>
+      <c r="G60" s="8">
+        <v>3</v>
+      </c>
+      <c r="H60" s="8">
+        <v>150</v>
+      </c>
+      <c r="I60" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="9" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J60" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="10"/>
-      <c r="L60" s="10"/>
-      <c r="M60" s="10"/>
+        <v>330</v>
+      </c>
+      <c r="K60" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L60" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="675" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA215080-4127-42AE-99BD-1A0BBDB3E1B0}"/>
+  <xr:revisionPtr revIDLastSave="687" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF5D017C-1266-45CA-9AFA-52D648EE8D20}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3633,25 +3633,47 @@
       <c r="N60" s="11"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="12"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
-      <c r="F61" s="8"/>
-      <c r="G61" s="8"/>
-      <c r="H61" s="8"/>
-      <c r="I61" s="9" t="str">
+      <c r="A61" s="12">
+        <v>46302</v>
+      </c>
+      <c r="B61" s="8">
+        <v>480</v>
+      </c>
+      <c r="C61" s="8">
+        <v>60</v>
+      </c>
+      <c r="D61" s="8">
+        <v>180</v>
+      </c>
+      <c r="E61" s="8">
+        <v>60</v>
+      </c>
+      <c r="F61" s="8">
+        <v>400</v>
+      </c>
+      <c r="G61" s="8">
+        <v>8</v>
+      </c>
+      <c r="H61" s="8">
+        <v>100</v>
+      </c>
+      <c r="I61" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="9" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J61" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="10"/>
-      <c r="L61" s="10"/>
-      <c r="M61" s="10"/>
+        <v>160</v>
+      </c>
+      <c r="K61" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L61" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="687" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF5D017C-1266-45CA-9AFA-52D648EE8D20}"/>
+  <xr:revisionPtr revIDLastSave="800" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9108714-D496-43AE-9DC9-5F7662BD43E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3677,201 +3677,399 @@
       <c r="N61" s="11"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="12"/>
-      <c r="B62" s="8"/>
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
-      <c r="F62" s="8"/>
-      <c r="G62" s="8"/>
-      <c r="H62" s="8"/>
-      <c r="I62" s="9" t="str">
+      <c r="A62" s="12">
+        <v>46303</v>
+      </c>
+      <c r="B62" s="8">
+        <v>480</v>
+      </c>
+      <c r="C62" s="8">
+        <v>60</v>
+      </c>
+      <c r="D62" s="8">
+        <v>180</v>
+      </c>
+      <c r="E62" s="8">
+        <v>60</v>
+      </c>
+      <c r="F62" s="8">
+        <v>300</v>
+      </c>
+      <c r="G62" s="8">
+        <v>5</v>
+      </c>
+      <c r="H62" s="8">
+        <v>200</v>
+      </c>
+      <c r="I62" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="9" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J62" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="10"/>
-      <c r="L62" s="10"/>
-      <c r="M62" s="10"/>
+        <v>160</v>
+      </c>
+      <c r="K62" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L62" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N62" s="11"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="12"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="9" t="str">
+      <c r="A63" s="12">
+        <v>46304</v>
+      </c>
+      <c r="B63" s="8">
+        <v>480</v>
+      </c>
+      <c r="C63" s="8">
+        <v>60</v>
+      </c>
+      <c r="D63" s="8">
+        <v>180</v>
+      </c>
+      <c r="E63" s="8">
+        <v>60</v>
+      </c>
+      <c r="F63" s="8">
+        <v>300</v>
+      </c>
+      <c r="G63" s="8">
+        <v>5</v>
+      </c>
+      <c r="H63" s="8">
+        <v>200</v>
+      </c>
+      <c r="I63" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="9" t="str">
+        <v>1280</v>
+      </c>
+      <c r="J63" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="10"/>
-      <c r="L63" s="10"/>
-      <c r="M63" s="10"/>
+        <v>160</v>
+      </c>
+      <c r="K63" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L63" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M63" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N63" s="11"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A64" s="12"/>
-      <c r="B64" s="8"/>
-      <c r="C64" s="8"/>
-      <c r="D64" s="8"/>
-      <c r="E64" s="8"/>
-      <c r="F64" s="8"/>
-      <c r="G64" s="8"/>
-      <c r="H64" s="8"/>
-      <c r="I64" s="9" t="str">
+      <c r="A64" s="12">
+        <v>46305</v>
+      </c>
+      <c r="B64" s="8">
+        <v>480</v>
+      </c>
+      <c r="C64" s="8">
+        <v>60</v>
+      </c>
+      <c r="D64" s="8">
+        <v>180</v>
+      </c>
+      <c r="E64" s="8">
+        <v>60</v>
+      </c>
+      <c r="F64" s="8">
+        <v>0</v>
+      </c>
+      <c r="G64" s="8">
+        <v>0</v>
+      </c>
+      <c r="H64" s="8">
+        <v>400</v>
+      </c>
+      <c r="I64" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J64" s="9" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J64" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K64" s="10"/>
-      <c r="L64" s="10"/>
-      <c r="M64" s="10"/>
+        <v>260</v>
+      </c>
+      <c r="K64" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L64" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M64" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N64" s="11"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="12"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
-      <c r="D65" s="8"/>
-      <c r="E65" s="8"/>
-      <c r="F65" s="8"/>
-      <c r="G65" s="8"/>
-      <c r="H65" s="8"/>
-      <c r="I65" s="9" t="str">
+      <c r="A65" s="12">
+        <v>46306</v>
+      </c>
+      <c r="B65" s="8">
+        <v>420</v>
+      </c>
+      <c r="C65" s="8">
+        <v>60</v>
+      </c>
+      <c r="D65" s="8">
+        <v>300</v>
+      </c>
+      <c r="E65" s="8">
+        <v>70</v>
+      </c>
+      <c r="F65" s="8">
+        <v>0</v>
+      </c>
+      <c r="G65" s="8">
+        <v>0</v>
+      </c>
+      <c r="H65" s="8">
+        <v>200</v>
+      </c>
+      <c r="I65" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="9" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J65" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="10"/>
-      <c r="L65" s="10"/>
-      <c r="M65" s="10"/>
+        <v>390</v>
+      </c>
+      <c r="K65" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L65" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M65" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N65" s="11"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="12"/>
-      <c r="B66" s="8"/>
-      <c r="C66" s="8"/>
-      <c r="D66" s="8"/>
-      <c r="E66" s="8"/>
-      <c r="F66" s="8"/>
-      <c r="G66" s="8"/>
-      <c r="H66" s="8"/>
-      <c r="I66" s="9" t="str">
+      <c r="A66" s="12">
+        <v>46307</v>
+      </c>
+      <c r="B66" s="8">
+        <v>400</v>
+      </c>
+      <c r="C66" s="8">
+        <v>60</v>
+      </c>
+      <c r="D66" s="8">
+        <v>360</v>
+      </c>
+      <c r="E66" s="8">
+        <v>40</v>
+      </c>
+      <c r="F66" s="8">
+        <v>0</v>
+      </c>
+      <c r="G66" s="8">
+        <v>0</v>
+      </c>
+      <c r="H66" s="8">
+        <v>200</v>
+      </c>
+      <c r="I66" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="9" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J66" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="10"/>
-      <c r="L66" s="10"/>
-      <c r="M66" s="10"/>
+        <v>380</v>
+      </c>
+      <c r="K66" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L66" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M66" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N66" s="11"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="12"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
-      <c r="D67" s="8"/>
-      <c r="E67" s="8"/>
-      <c r="F67" s="8"/>
-      <c r="G67" s="8"/>
-      <c r="H67" s="8"/>
-      <c r="I67" s="9" t="str">
+      <c r="A67" s="12">
+        <v>46308</v>
+      </c>
+      <c r="B67" s="8">
+        <v>360</v>
+      </c>
+      <c r="C67" s="8">
+        <v>60</v>
+      </c>
+      <c r="D67" s="8">
+        <v>480</v>
+      </c>
+      <c r="E67" s="8">
+        <v>40</v>
+      </c>
+      <c r="F67" s="8">
+        <v>0</v>
+      </c>
+      <c r="G67" s="8">
+        <v>0</v>
+      </c>
+      <c r="H67" s="8">
+        <v>200</v>
+      </c>
+      <c r="I67" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="9" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J67" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="10"/>
-      <c r="L67" s="10"/>
-      <c r="M67" s="10"/>
+        <v>300</v>
+      </c>
+      <c r="K67" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L67" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M67" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N67" s="11"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="12"/>
-      <c r="B68" s="8"/>
-      <c r="C68" s="8"/>
-      <c r="D68" s="8"/>
-      <c r="E68" s="8"/>
-      <c r="F68" s="8"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="9" t="str">
+      <c r="A68" s="12">
+        <v>46309</v>
+      </c>
+      <c r="B68" s="8">
+        <v>360</v>
+      </c>
+      <c r="C68" s="8">
+        <v>60</v>
+      </c>
+      <c r="D68" s="8">
+        <v>480</v>
+      </c>
+      <c r="E68" s="8">
+        <v>60</v>
+      </c>
+      <c r="F68" s="8">
+        <v>0</v>
+      </c>
+      <c r="G68" s="8">
+        <v>0</v>
+      </c>
+      <c r="H68" s="8">
+        <v>200</v>
+      </c>
+      <c r="I68" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="9" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J68" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="10"/>
-      <c r="L68" s="10"/>
-      <c r="M68" s="10"/>
+        <v>280</v>
+      </c>
+      <c r="K68" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L68" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M68" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N68" s="11"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="12"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
-      <c r="D69" s="8"/>
-      <c r="E69" s="8"/>
-      <c r="F69" s="8"/>
-      <c r="G69" s="8"/>
-      <c r="H69" s="8"/>
-      <c r="I69" s="9" t="str">
+      <c r="A69" s="12">
+        <v>46310</v>
+      </c>
+      <c r="B69" s="8">
+        <v>360</v>
+      </c>
+      <c r="C69" s="8">
+        <v>60</v>
+      </c>
+      <c r="D69" s="8">
+        <v>300</v>
+      </c>
+      <c r="E69" s="8">
+        <v>60</v>
+      </c>
+      <c r="F69" s="8">
+        <v>0</v>
+      </c>
+      <c r="G69" s="8">
+        <v>0</v>
+      </c>
+      <c r="H69" s="8">
+        <v>300</v>
+      </c>
+      <c r="I69" s="9">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="9" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J69" s="9">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="10"/>
-      <c r="L69" s="10"/>
-      <c r="M69" s="10"/>
+        <v>360</v>
+      </c>
+      <c r="K69" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L69" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M69" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N69" s="11"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="12"/>
-      <c r="B70" s="8"/>
-      <c r="C70" s="8"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="8"/>
-      <c r="F70" s="8"/>
-      <c r="G70" s="8"/>
-      <c r="H70" s="8"/>
-      <c r="I70" s="9" t="str">
+      <c r="A70" s="12">
+        <v>46311</v>
+      </c>
+      <c r="B70" s="8">
+        <v>360</v>
+      </c>
+      <c r="C70" s="8">
+        <v>60</v>
+      </c>
+      <c r="D70" s="8">
+        <v>300</v>
+      </c>
+      <c r="E70" s="8">
+        <v>70</v>
+      </c>
+      <c r="F70" s="8">
+        <v>0</v>
+      </c>
+      <c r="G70" s="8">
+        <v>0</v>
+      </c>
+      <c r="H70" s="8">
+        <v>300</v>
+      </c>
+      <c r="I70" s="9">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="9" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J70" s="9">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="10"/>
-      <c r="L70" s="10"/>
-      <c r="M70" s="10"/>
+        <v>350</v>
+      </c>
+      <c r="K70" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L70" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M70" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N70" s="11"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="800" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9108714-D496-43AE-9DC9-5F7662BD43E7}"/>
+  <xr:revisionPtr revIDLastSave="816" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D2E9AA-6524-4A88-B923-4894D96D3D33}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4073,25 +4073,47 @@
       <c r="N70" s="11"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="12"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
-      <c r="D71" s="8"/>
-      <c r="E71" s="8"/>
-      <c r="F71" s="8"/>
-      <c r="G71" s="8"/>
-      <c r="H71" s="8"/>
-      <c r="I71" s="9" t="str">
+      <c r="A71" s="12">
+        <v>46311</v>
+      </c>
+      <c r="B71" s="8">
+        <v>360</v>
+      </c>
+      <c r="C71" s="8">
+        <v>60</v>
+      </c>
+      <c r="D71" s="8">
+        <v>200</v>
+      </c>
+      <c r="E71" s="8">
+        <v>70</v>
+      </c>
+      <c r="F71" s="8">
+        <v>300</v>
+      </c>
+      <c r="G71" s="8">
+        <v>5</v>
+      </c>
+      <c r="H71" s="8">
+        <v>200</v>
+      </c>
+      <c r="I71" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="9" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J71" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="10"/>
-      <c r="L71" s="10"/>
-      <c r="M71" s="10"/>
+        <v>250</v>
+      </c>
+      <c r="K71" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N71" s="11"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="816" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A9D2E9AA-6524-4A88-B923-4894D96D3D33}"/>
+  <xr:revisionPtr revIDLastSave="881" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72840913-2A22-45E7-8EE2-12862CC40E9B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4074,7 +4074,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="12">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="B71" s="8">
         <v>360</v>
@@ -4089,21 +4089,21 @@
         <v>70</v>
       </c>
       <c r="F71" s="8">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G71" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H71" s="8">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="I71" s="9">
         <f t="shared" si="2"/>
-        <v>1190</v>
+        <v>1090</v>
       </c>
       <c r="J71" s="9">
         <f t="shared" si="3"/>
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="K71" s="10" t="s">
         <v>40</v>
@@ -4117,113 +4117,223 @@
       <c r="N71" s="11"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="12"/>
-      <c r="B72" s="8"/>
-      <c r="C72" s="8"/>
-      <c r="D72" s="8"/>
-      <c r="E72" s="8"/>
-      <c r="F72" s="8"/>
-      <c r="G72" s="8"/>
-      <c r="H72" s="8"/>
-      <c r="I72" s="9" t="str">
+      <c r="A72" s="12">
+        <v>46313</v>
+      </c>
+      <c r="B72" s="8">
+        <v>480</v>
+      </c>
+      <c r="C72" s="8">
+        <v>75</v>
+      </c>
+      <c r="D72" s="8">
+        <v>180</v>
+      </c>
+      <c r="E72" s="8">
+        <v>60</v>
+      </c>
+      <c r="F72" s="8">
+        <v>0</v>
+      </c>
+      <c r="G72" s="8">
+        <v>0</v>
+      </c>
+      <c r="H72" s="8">
+        <v>400</v>
+      </c>
+      <c r="I72" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="9" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J72" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="10"/>
-      <c r="L72" s="10"/>
-      <c r="M72" s="10"/>
+        <v>245</v>
+      </c>
+      <c r="K72" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="L72" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M72" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N72" s="11"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="12"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
-      <c r="D73" s="8"/>
-      <c r="E73" s="8"/>
-      <c r="F73" s="8"/>
-      <c r="G73" s="8"/>
-      <c r="H73" s="8"/>
-      <c r="I73" s="9" t="str">
+      <c r="A73" s="12">
+        <v>46314</v>
+      </c>
+      <c r="B73" s="8">
+        <v>420</v>
+      </c>
+      <c r="C73" s="8">
+        <v>60</v>
+      </c>
+      <c r="D73" s="8">
+        <v>180</v>
+      </c>
+      <c r="E73" s="8">
+        <v>60</v>
+      </c>
+      <c r="F73" s="8">
+        <v>300</v>
+      </c>
+      <c r="G73" s="8">
+        <v>6</v>
+      </c>
+      <c r="H73" s="8">
+        <v>180</v>
+      </c>
+      <c r="I73" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="9" t="str">
+        <v>1200</v>
+      </c>
+      <c r="J73" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="10"/>
-      <c r="L73" s="10"/>
-      <c r="M73" s="10"/>
+        <v>240</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="L73" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="M73" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="N73" s="11"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="12"/>
-      <c r="B74" s="8"/>
-      <c r="C74" s="8"/>
-      <c r="D74" s="8"/>
-      <c r="E74" s="8"/>
-      <c r="F74" s="8"/>
-      <c r="G74" s="8"/>
-      <c r="H74" s="8"/>
-      <c r="I74" s="9" t="str">
+      <c r="A74" s="12">
+        <v>46315</v>
+      </c>
+      <c r="B74" s="8">
+        <v>420</v>
+      </c>
+      <c r="C74" s="8">
+        <v>60</v>
+      </c>
+      <c r="D74" s="8">
+        <v>180</v>
+      </c>
+      <c r="E74" s="8">
+        <v>60</v>
+      </c>
+      <c r="F74" s="8">
+        <v>0</v>
+      </c>
+      <c r="G74" s="8">
+        <v>0</v>
+      </c>
+      <c r="H74" s="8">
+        <v>400</v>
+      </c>
+      <c r="I74" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="9" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J74" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="10"/>
-      <c r="L74" s="10"/>
-      <c r="M74" s="10"/>
+        <v>320</v>
+      </c>
+      <c r="K74" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L74" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M74" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N74" s="11"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="12"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
-      <c r="D75" s="8"/>
-      <c r="E75" s="8"/>
-      <c r="F75" s="8"/>
-      <c r="G75" s="8"/>
-      <c r="H75" s="8"/>
-      <c r="I75" s="9" t="str">
+      <c r="A75" s="12">
+        <v>46316</v>
+      </c>
+      <c r="B75" s="8">
+        <v>420</v>
+      </c>
+      <c r="C75" s="8">
+        <v>60</v>
+      </c>
+      <c r="D75" s="8">
+        <v>200</v>
+      </c>
+      <c r="E75" s="8">
+        <v>60</v>
+      </c>
+      <c r="F75" s="8">
+        <v>400</v>
+      </c>
+      <c r="G75" s="8">
+        <v>8</v>
+      </c>
+      <c r="H75" s="8">
+        <v>100</v>
+      </c>
+      <c r="I75" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="9" t="str">
+        <v>1240</v>
+      </c>
+      <c r="J75" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="10"/>
-      <c r="L75" s="10"/>
-      <c r="M75" s="10"/>
+        <v>200</v>
+      </c>
+      <c r="K75" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L75" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M75" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N75" s="11"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="12"/>
-      <c r="B76" s="8"/>
-      <c r="C76" s="8"/>
-      <c r="D76" s="8"/>
-      <c r="E76" s="8"/>
-      <c r="F76" s="8"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="9" t="str">
+      <c r="A76" s="12">
+        <v>46317</v>
+      </c>
+      <c r="B76" s="8">
+        <v>420</v>
+      </c>
+      <c r="C76" s="8">
+        <v>60</v>
+      </c>
+      <c r="D76" s="8">
+        <v>200</v>
+      </c>
+      <c r="E76" s="8">
+        <v>60</v>
+      </c>
+      <c r="F76" s="8">
+        <v>250</v>
+      </c>
+      <c r="G76" s="8">
+        <v>5</v>
+      </c>
+      <c r="H76" s="8">
+        <v>150</v>
+      </c>
+      <c r="I76" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="9" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J76" s="9">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="10"/>
-      <c r="L76" s="10"/>
-      <c r="M76" s="10"/>
+        <v>300</v>
+      </c>
+      <c r="K76" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L76" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M76" s="10" t="s">
+        <v>42</v>
+      </c>
       <c r="N76" s="11"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="881" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72840913-2A22-45E7-8EE2-12862CC40E9B}"/>
+  <xr:revisionPtr revIDLastSave="883" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE305D3-C2E3-42C3-A4CE-0B26F66013AD}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4337,21 +4337,25 @@
       <c r="N76" s="11"/>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="12"/>
-      <c r="B77" s="8"/>
+      <c r="A77" s="12">
+        <v>46318</v>
+      </c>
+      <c r="B77" s="8">
+        <v>360</v>
+      </c>
       <c r="C77" s="8"/>
       <c r="D77" s="8"/>
       <c r="E77" s="8"/>
       <c r="F77" s="8"/>
       <c r="G77" s="8"/>
       <c r="H77" s="8"/>
-      <c r="I77" s="9" t="str">
+      <c r="I77" s="9">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="9" t="str">
+        <v>360</v>
+      </c>
+      <c r="J77" s="9">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1080</v>
       </c>
       <c r="K77" s="10"/>
       <c r="L77" s="10"/>

--- a/12627223.xlsx
+++ b/12627223.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/51195193784e6159/Desktop/pyxls/CAP776/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="883" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6DE305D3-C2E3-42C3-A4CE-0B26F66013AD}"/>
+  <xr:revisionPtr revIDLastSave="892" documentId="11_A8BFE1085DD30652DF65CA6AB960F4CDB8B087FB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB2F7876-E520-41FE-98FD-DD65E48671DE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4343,23 +4343,41 @@
       <c r="B77" s="8">
         <v>360</v>
       </c>
-      <c r="C77" s="8"/>
-      <c r="D77" s="8"/>
-      <c r="E77" s="8"/>
-      <c r="F77" s="8"/>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
+      <c r="C77" s="8">
+        <v>60</v>
+      </c>
+      <c r="D77" s="8">
+        <v>200</v>
+      </c>
+      <c r="E77" s="8">
+        <v>60</v>
+      </c>
+      <c r="F77" s="8">
+        <v>250</v>
+      </c>
+      <c r="G77" s="8">
+        <v>5</v>
+      </c>
+      <c r="H77" s="8">
+        <v>200</v>
+      </c>
       <c r="I77" s="9">
         <f t="shared" si="2"/>
-        <v>360</v>
+        <v>1130</v>
       </c>
       <c r="J77" s="9">
         <f t="shared" si="3"/>
-        <v>1080</v>
-      </c>
-      <c r="K77" s="10"/>
-      <c r="L77" s="10"/>
-      <c r="M77" s="10"/>
+        <v>310</v>
+      </c>
+      <c r="K77" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="L77" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="M77" s="10" t="s">
+        <v>46</v>
+      </c>
       <c r="N77" s="11"/>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
